--- a/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
+++ b/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\WebAppCoding\WebAppCoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9A5AB5-9F49-4083-B995-48D4ABC7BE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8A7114-E6F3-48FC-A541-93BCE23E759B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="10" sheetId="1" r:id="rId1"/>
-    <sheet name="11" sheetId="2" r:id="rId2"/>
-    <sheet name="12" sheetId="3" r:id="rId3"/>
-    <sheet name="13" sheetId="4" r:id="rId4"/>
-    <sheet name="14" sheetId="5" r:id="rId5"/>
-    <sheet name="15" sheetId="6" r:id="rId6"/>
-    <sheet name="16" sheetId="7" r:id="rId7"/>
-    <sheet name="17" sheetId="8" r:id="rId8"/>
-    <sheet name="19" sheetId="9" r:id="rId9"/>
-    <sheet name="20" sheetId="10" r:id="rId10"/>
-    <sheet name="21" sheetId="11" r:id="rId11"/>
-    <sheet name="22" sheetId="12" r:id="rId12"/>
+    <sheet name="Chapter" sheetId="13" r:id="rId1"/>
+    <sheet name="10" sheetId="1" r:id="rId2"/>
+    <sheet name="11" sheetId="2" r:id="rId3"/>
+    <sheet name="12" sheetId="3" r:id="rId4"/>
+    <sheet name="13" sheetId="4" r:id="rId5"/>
+    <sheet name="14" sheetId="5" r:id="rId6"/>
+    <sheet name="15" sheetId="6" r:id="rId7"/>
+    <sheet name="16" sheetId="7" r:id="rId8"/>
+    <sheet name="17" sheetId="8" r:id="rId9"/>
+    <sheet name="19" sheetId="9" r:id="rId10"/>
+    <sheet name="20" sheetId="10" r:id="rId11"/>
+    <sheet name="21" sheetId="11" r:id="rId12"/>
+    <sheet name="22" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="531">
   <si>
     <t>10 .Text Box</t>
   </si>
@@ -2508,6 +2509,522 @@
   </si>
   <si>
     <t>Now if we select the first dropdown then dropdown should be enable</t>
+  </si>
+  <si>
+    <t>1. What is ASP.NET</t>
+  </si>
+  <si>
+    <t>2. Creating your first ASP.NET website</t>
+  </si>
+  <si>
+    <t>3. What is viewstate</t>
+  </si>
+  <si>
+    <t>4. Events in the life cycle of a web application</t>
+  </si>
+  <si>
+    <t>5. Difference between ViewState, SessionState and ApplicationState in asp.net</t>
+  </si>
+  <si>
+    <t>6. ASP.NET Page Life Cycle Events</t>
+  </si>
+  <si>
+    <t>7. ASP.NET Server control events</t>
+  </si>
+  <si>
+    <t>8. IsPostBack in ASP.NET</t>
+  </si>
+  <si>
+    <t>9. IIS - Internet Information Services and ASP.NET</t>
+  </si>
+  <si>
+    <t>10. ASP.NET TextBox Control</t>
+  </si>
+  <si>
+    <t>11. Radio Button Control</t>
+  </si>
+  <si>
+    <t>12. CheckBox Control</t>
+  </si>
+  <si>
+    <t>13. HyperLink Control</t>
+  </si>
+  <si>
+    <t>14. Button, LinkButton and ImageButton Controls</t>
+  </si>
+  <si>
+    <t>15. Command Event of an asp.net button control</t>
+  </si>
+  <si>
+    <t>16. Dropdownlist in asp.net</t>
+  </si>
+  <si>
+    <t>17. Data bind asp.net dropdownlist with data from the database</t>
+  </si>
+  <si>
+    <t>18. Binding an asp.net dropdownlist with an XML file</t>
+  </si>
+  <si>
+    <t>19. Mapping virtual path to physical path using Server.MapPath method</t>
+  </si>
+  <si>
+    <t>20. Mapping virtual path to physical path using Server.MapPath method Example</t>
+  </si>
+  <si>
+    <t>21. Retrieving selected item text value and index of dropdownlist</t>
+  </si>
+  <si>
+    <t>22. Cascading dropdown in asp.net</t>
+  </si>
+  <si>
+    <t>23. ASP.NET CheckBoxList Control</t>
+  </si>
+  <si>
+    <t>24. ASP.NET CheckBoxList, Select or Deselect all list items</t>
+  </si>
+  <si>
+    <t>25. ASP.NET ListBox control</t>
+  </si>
+  <si>
+    <t>26. ASP.NET CheckBoxList and ListBox real time example</t>
+  </si>
+  <si>
+    <t>27. ASP.NET RadioButtonList control</t>
+  </si>
+  <si>
+    <t>28. Bulleted list in asp.net</t>
+  </si>
+  <si>
+    <t>29. List controls in asp.net</t>
+  </si>
+  <si>
+    <t>30. Fileupload control in asp.net</t>
+  </si>
+  <si>
+    <t>31. Adrotator control in asp.net</t>
+  </si>
+  <si>
+    <t>32. Asp.net calendar control</t>
+  </si>
+  <si>
+    <t>33. Asp.net calendar control properties and events</t>
+  </si>
+  <si>
+    <t>34. Hidden field in asp.net</t>
+  </si>
+  <si>
+    <t>35. Multiview control in asp.net</t>
+  </si>
+  <si>
+    <t>36. Wizard control in asp.net</t>
+  </si>
+  <si>
+    <t>37. Asp.net Wizard control properties</t>
+  </si>
+  <si>
+    <t>38. Asp.net Wizard control events</t>
+  </si>
+  <si>
+    <t>39. UseSubmitBehavior property of the Button control</t>
+  </si>
+  <si>
+    <t>40. Asp.net wizard control templates</t>
+  </si>
+  <si>
+    <t>41. Literal control in asp.net</t>
+  </si>
+  <si>
+    <t>42. Asp.net panel control</t>
+  </si>
+  <si>
+    <t>43. Creating controls dynamically using asp.net panel control</t>
+  </si>
+  <si>
+    <t>44. RequiredField validator control in asp.net</t>
+  </si>
+  <si>
+    <t>45. Rangevalidator control in asp.net</t>
+  </si>
+  <si>
+    <t>46. CompareValidator control in asp.net</t>
+  </si>
+  <si>
+    <t>47. RegularExpressionValidator control in asp.net</t>
+  </si>
+  <si>
+    <t>48. CustomValidator control in asp.net</t>
+  </si>
+  <si>
+    <t>49. ValidationSummary control in asp.net</t>
+  </si>
+  <si>
+    <t>50. ValidationGroups in asp.net</t>
+  </si>
+  <si>
+    <t>51. Different page navigation techniques</t>
+  </si>
+  <si>
+    <t>52. Response.Redirect in asp.net</t>
+  </si>
+  <si>
+    <t>53. Server.Transfer in asp.net</t>
+  </si>
+  <si>
+    <t>54. Server.execute in asp.net</t>
+  </si>
+  <si>
+    <t>55. Cross page posting in asp.net</t>
+  </si>
+  <si>
+    <t>56. Cross page postback strongly typed reference</t>
+  </si>
+  <si>
+    <t>57. Opening new window using javascript in asp.net</t>
+  </si>
+  <si>
+    <t>58. Techniques to send data from one webform to another</t>
+  </si>
+  <si>
+    <t>59. QueryString in asp.net</t>
+  </si>
+  <si>
+    <t>60. Cookies in asp.net</t>
+  </si>
+  <si>
+    <t>61. How to Check if cookies are enabled or disabled</t>
+  </si>
+  <si>
+    <t>62. Asp.net session state</t>
+  </si>
+  <si>
+    <t>63. Cookie less sessions in asp.net</t>
+  </si>
+  <si>
+    <t>64. Inporc asp.net session state mode management</t>
+  </si>
+  <si>
+    <t>65. StateServer asp.net session state mode management</t>
+  </si>
+  <si>
+    <t>66. SQLServer asp.net session state mode management</t>
+  </si>
+  <si>
+    <t>67. Asp.net Application state</t>
+  </si>
+  <si>
+    <t>68. Asp.net application state real time example</t>
+  </si>
+  <si>
+    <t>69. Exception handling in asp.net</t>
+  </si>
+  <si>
+    <t>70. Error events</t>
+  </si>
+  <si>
+    <t>71. Custom errors</t>
+  </si>
+  <si>
+    <t>72. Windows event viewer</t>
+  </si>
+  <si>
+    <t>73. Logging exceptions to the windows eventviewer</t>
+  </si>
+  <si>
+    <t>74. Logging exceptions as information entry type in windows eventviewer</t>
+  </si>
+  <si>
+    <t>75. Logging exception to database</t>
+  </si>
+  <si>
+    <t>76. Customizing asp.net exception Logging</t>
+  </si>
+  <si>
+    <t>77. Sending emails using asp.net</t>
+  </si>
+  <si>
+    <t>78. Sending emails in asp.net using SMTP server settings from web.config</t>
+  </si>
+  <si>
+    <t>79. Tracing</t>
+  </si>
+  <si>
+    <t>80. Writing custom asp.net tracing messages</t>
+  </si>
+  <si>
+    <t>81. Tracing in asp.net - A real time example</t>
+  </si>
+  <si>
+    <t>82. Application pool in IIS</t>
+  </si>
+  <si>
+    <t>83. Applications isolation using application pools</t>
+  </si>
+  <si>
+    <t>84. Application pools in IIS Security</t>
+  </si>
+  <si>
+    <t>85. Anonymous authentication</t>
+  </si>
+  <si>
+    <t>86. Anonymous authentication and impersonation</t>
+  </si>
+  <si>
+    <t>87. Windows authentication</t>
+  </si>
+  <si>
+    <t>88. Windows authentication and authorization</t>
+  </si>
+  <si>
+    <t>89. Windows authentication and folder level authorization</t>
+  </si>
+  <si>
+    <t>90. Forms authentication using user names list in web.config</t>
+  </si>
+  <si>
+    <t>91. Forms authentication in asp.net and user registration</t>
+  </si>
+  <si>
+    <t>92. Forms authentication against users in database table</t>
+  </si>
+  <si>
+    <t>93. Forms authentication and locking user accounts</t>
+  </si>
+  <si>
+    <t>94. Unlocking the locked user accounts</t>
+  </si>
+  <si>
+    <t>95. Implementing password reset link in asp.net</t>
+  </si>
+  <si>
+    <t>96. Implementing change password page</t>
+  </si>
+  <si>
+    <t>97. Changing password by providing current password</t>
+  </si>
+  <si>
+    <t>98. Unlocking the locked user accounts using a web page</t>
+  </si>
+  <si>
+    <t>99. Implementing Enable button to unlock user accounts</t>
+  </si>
+  <si>
+    <t>100. Secure Socket Layer</t>
+  </si>
+  <si>
+    <t>101. Implementing SSL in asp.net web application</t>
+  </si>
+  <si>
+    <t>102. Redirect http to https in IIS using URL ReWrite module</t>
+  </si>
+  <si>
+    <t>103. Redirect http to https in iis using custom errors</t>
+  </si>
+  <si>
+    <t>104. User controls</t>
+  </si>
+  <si>
+    <t>105. Adding and using user controls on a webform</t>
+  </si>
+  <si>
+    <t>106. Raising custom events from user controls</t>
+  </si>
+  <si>
+    <t>107. Consuming user control custom events</t>
+  </si>
+  <si>
+    <t>108. Events and delegates</t>
+  </si>
+  <si>
+    <t>109. Loading user controls dynamically</t>
+  </si>
+  <si>
+    <t>110. Loading controls dynamically in ASP.NET</t>
+  </si>
+  <si>
+    <t>111. Navigating to a specific month and an year in an asp.net calendar control</t>
+  </si>
+  <si>
+    <t>112. ASP.NET custom server controls</t>
+  </si>
+  <si>
+    <t>113. Adding composite custom controls to visual studio tool box</t>
+  </si>
+  <si>
+    <t>114. Adding properties to composite custom controls</t>
+  </si>
+  <si>
+    <t>115. Solving the problems of asp.net composite custom calendar control</t>
+  </si>
+  <si>
+    <t>116. Adding custom events to asp.net composite custom control</t>
+  </si>
+  <si>
+    <t>117. Assigning an image to the composite custom control in visual studio tool box</t>
+  </si>
+  <si>
+    <t>118. Difference between user controls and custom controls</t>
+  </si>
+  <si>
+    <t>119. Caching in asp.net</t>
+  </si>
+  <si>
+    <t>120. Caching multiple responses for a single webform</t>
+  </si>
+  <si>
+    <t>121. Controlling asp.net caching in code</t>
+  </si>
+  <si>
+    <t>122. Fragment caching in asp.net</t>
+  </si>
+  <si>
+    <t>123. Web form caching based on GET and POST requests</t>
+  </si>
+  <si>
+    <t>124. Caching multiple versions of user control using VaryByControl</t>
+  </si>
+  <si>
+    <t>125. Caching multiple versions of user control using VaryByParam</t>
+  </si>
+  <si>
+    <t>126. Caching application data in asp.net</t>
+  </si>
+  <si>
+    <t>127. Different ways to cache application data in asp.net</t>
+  </si>
+  <si>
+    <t>128. Caching in asp.net - AbsoluteExpiration, SlidingExpiration, and CacheItemPriority</t>
+  </si>
+  <si>
+    <t>129. Cache dependency on files in asp.net</t>
+  </si>
+  <si>
+    <t>130. Reloading or refreshing cache automatically, when cached data is removed</t>
+  </si>
+  <si>
+    <t>131. Cache dependency on sql server database table</t>
+  </si>
+  <si>
+    <t>132. Reload data into cache automatically when data in the table changes</t>
+  </si>
+  <si>
+    <t>133. What is AutoEventWireup in asp.net</t>
+  </si>
+  <si>
+    <t>134. Add image slideshow to your website using asp.net ajax and c#</t>
+  </si>
+  <si>
+    <t>135. Display images in sequence in an image slideshow</t>
+  </si>
+  <si>
+    <t>136. Provide capability to start and stop image slideshow</t>
+  </si>
+  <si>
+    <t>137. Add images to slideshow using xml file</t>
+  </si>
+  <si>
+    <t>138. Add images to slideshow using database table</t>
+  </si>
+  <si>
+    <t>139. How to upload and download files</t>
+  </si>
+  <si>
+    <t>140. Creating an image gallery using asp.net and c#</t>
+  </si>
+  <si>
+    <t>141. Contact us page using asp.net and c#</t>
+  </si>
+  <si>
+    <t>142. Contact us page using asp.net and c# continued</t>
+  </si>
+  <si>
+    <t>143. Difference between http get and http post methods</t>
+  </si>
+  <si>
+    <t>144. How to check if the request method is a GET or a POST in MVC</t>
+  </si>
+  <si>
+    <t>145. Implementing autocomplete textbox in asp.net web forms</t>
+  </si>
+  <si>
+    <t>146. Why use master pages in asp.net</t>
+  </si>
+  <si>
+    <t>147. Master pages in asp.net</t>
+  </si>
+  <si>
+    <t>148. Passing data from content page to master page</t>
+  </si>
+  <si>
+    <t>149. Passing data from master page to content page</t>
+  </si>
+  <si>
+    <t>150. Default content in contentplaceholder of a master page</t>
+  </si>
+  <si>
+    <t>151. Assigning a master page dynamically</t>
+  </si>
+  <si>
+    <t>152. Master page content page user control life cycle</t>
+  </si>
+  <si>
+    <t>153. Menu control in asp.net</t>
+  </si>
+  <si>
+    <t>154. Using styles with asp.net menu control</t>
+  </si>
+  <si>
+    <t>155. Binding menu control to xml file</t>
+  </si>
+  <si>
+    <t>156. Binding menu control to database table</t>
+  </si>
+  <si>
+    <t>157. SiteMapPath control in asp.net</t>
+  </si>
+  <si>
+    <t>158. Binding menu control to web.sitemap file</t>
+  </si>
+  <si>
+    <t>159. TreeView control in asp.net</t>
+  </si>
+  <si>
+    <t>160. Binding treeview control to an xml file</t>
+  </si>
+  <si>
+    <t>161. Binding treeview control to web.sitemap file</t>
+  </si>
+  <si>
+    <t>162. Binding asp.net treeview control to database table</t>
+  </si>
+  <si>
+    <t>163. Dynamically adding treenodes to treeview control</t>
+  </si>
+  <si>
+    <t>164. Displaying organization chart using treeview control</t>
+  </si>
+  <si>
+    <t>165. How to display an icon for website on browser tab</t>
+  </si>
+  <si>
+    <t>166. Captcha control in asp.net</t>
+  </si>
+  <si>
+    <t>167. Using ASP.NET validation controls with recaptcha</t>
+  </si>
+  <si>
+    <t>168. Customizing recaptcha control</t>
+  </si>
+  <si>
+    <t>169. Save image to database using asp.net</t>
+  </si>
+  <si>
+    <t>170. Load image from database in asp.net</t>
+  </si>
+  <si>
+    <t>171. How to show images from database in gridview in asp.net</t>
+  </si>
+  <si>
+    <t>172. Display data from two or more database table columns in asp.net dropdownlist</t>
   </si>
 </sst>
 </file>
@@ -2664,7 +3181,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2720,6 +3237,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8152,6 +8672,1713 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29D76A65-EE41-415B-A99C-810B3C929668}">
+  <dimension ref="B2:B173"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="80" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="20" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="20" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="20" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="20" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="20" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="20" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="20" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="20" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="20" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="20" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="20" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="20" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="20" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="20" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="20" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="20" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="20" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="20" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="20" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="20" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="20" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="20" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="20" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="20" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="20" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="20" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="20" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="20" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="20" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="20" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="20" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="20" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="20" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="20" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="20" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="20" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="20" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="20" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="20" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="20" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="20" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="20" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="20" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="20" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="20" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="20" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="20" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="20" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="20" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="20" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="20" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="20" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="20" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="20" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="20" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="20" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="20" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="20" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="20" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="20" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="20" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="20" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="20" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="20" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="20" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="20" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="20" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="20" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="20" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="20" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="20" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="20" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="20" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="20" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="20" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="20" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="20" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="20" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="20" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B91" s="20" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="20" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="20" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="20" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="20" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="20" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="20" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="20" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="20" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="20" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="20" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="20" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="20" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="20" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="20" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="20" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="20" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="20" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="20" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="20" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="20" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="20" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="20" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="20" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B116" s="20" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="20" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="20" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="20" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="20" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B121" s="20" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" s="20" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="20" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="20" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="20" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B126" s="20" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B127" s="20" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B128" s="20" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="20" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="20" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="20" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="20" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="20" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="20" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="20" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="20" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="20" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B138" s="20" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="20" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B140" s="20" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B141" s="20" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="20" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="20" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B144" s="20" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B145" s="20" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="20" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="20" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="20" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="20" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="20" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="20" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" s="20" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B153" s="20" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="20" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B155" s="20" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="20" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="20" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" s="20" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B159" s="20" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" s="20" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="20" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="20" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B163" s="20" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="20" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="20" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="20" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="20" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="20" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="20" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B170" s="20" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="20" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="20" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" s="20" t="s">
+        <v>530</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="http://csharp-video-tutorials.blogspot.com/2012/10/what-is-aspnet-part-1.html" xr:uid="{F3C3F2D2-CD2E-4EA9-AA63-BC2D417924B7}"/>
+    <hyperlink ref="B3" r:id="rId2" display="http://csharp-video-tutorials.blogspot.com/2012/10/creating-aspnet-website-part-2.html" xr:uid="{7640E163-9303-4E9E-9A9E-6F850CD29E4A}"/>
+    <hyperlink ref="B4" r:id="rId3" display="http://csharp-video-tutorials.blogspot.com/2012/10/what-is-viewstate-in-aspnet-part-3.html" xr:uid="{7644859B-2451-4A4B-984C-08CEA07BCBAE}"/>
+    <hyperlink ref="B5" r:id="rId4" display="http://csharp-video-tutorials.blogspot.com/2012/10/events-in-life-cycle-of-web-application.html" xr:uid="{9CCBD0F8-5DDD-4DBA-8884-F65E1E9BE1CA}"/>
+    <hyperlink ref="B6" r:id="rId5" display="http://csharp-video-tutorials.blogspot.com/2012/10/difference-between-viewstate-session.html" xr:uid="{F53FD386-4EE6-4049-919E-28A22A5F28CB}"/>
+    <hyperlink ref="B7" r:id="rId6" display="http://csharp-video-tutorials.blogspot.com/2012/10/aspnet-page-life-cycle-events-part-6.html" xr:uid="{B6D0241D-83A8-4E9E-B3F3-DE949934276A}"/>
+    <hyperlink ref="B8" r:id="rId7" display="http://csharp-video-tutorials.blogspot.com/2012/10/aspnet-server-control-events-part-7.html" xr:uid="{69E1C4BC-E1B0-4166-81D7-342669432831}"/>
+    <hyperlink ref="B9" r:id="rId8" display="http://csharp-video-tutorials.blogspot.com/2012/10/ispostback-in-aspnet-part-8.html" xr:uid="{4AE5A256-F89E-4E66-9457-03061BF63DFF}"/>
+    <hyperlink ref="B10" r:id="rId9" display="http://csharp-video-tutorials.blogspot.com/2012/10/iis-internet-information-services-and.html" xr:uid="{6C887AFF-4BB3-4866-9DF6-FF9826EE8AE4}"/>
+    <hyperlink ref="B11" r:id="rId10" display="http://csharp-video-tutorials.blogspot.com/2012/10/aspnet-textbox-control-part-10.html" xr:uid="{F01802DC-1627-45A8-89BE-C1C830BD0B9A}"/>
+    <hyperlink ref="B12" r:id="rId11" display="http://csharp-video-tutorials.blogspot.com/2012/10/aspnet-radio-button-control-part-11.html" xr:uid="{2EE14AC8-1141-4B35-BB22-35DF4A75BBEF}"/>
+    <hyperlink ref="B13" r:id="rId12" display="http://csharp-video-tutorials.blogspot.com/2012/10/aspnet-checkbox-control-part-12.html" xr:uid="{F55936B3-C960-444B-AA36-E44029541F1D}"/>
+    <hyperlink ref="B14" r:id="rId13" display="http://csharp-video-tutorials.blogspot.com/2012/10/aspnet-hyperlink-control-part-13.html" xr:uid="{354163D7-59BF-4500-8B1B-F175C76ACD61}"/>
+    <hyperlink ref="B15" r:id="rId14" display="http://csharp-video-tutorials.blogspot.com/2012/10/aspnet-button-linkbutton-and.html" xr:uid="{460ADB80-8F64-449E-95A8-BE9E63EA8A39}"/>
+    <hyperlink ref="B16" r:id="rId15" display="http://csharp-video-tutorials.blogspot.com/2012/10/command-event-of-aspnet-button-control.html" xr:uid="{9A24A1CA-2679-40AA-814C-B29B22F564A1}"/>
+    <hyperlink ref="B17" r:id="rId16" display="http://csharp-video-tutorials.blogspot.com/2012/10/dropdownlist-in-aspnet-part-16.html" xr:uid="{4A9E1457-BF52-459D-90BD-2D7AE7327D95}"/>
+    <hyperlink ref="B18" r:id="rId17" display="http://csharp-video-tutorials.blogspot.com/2012/11/data-bind-aspnet-dropdownlist-with-data.html" xr:uid="{77712AF4-B4ED-4C98-ADE1-89702E0EA2BA}"/>
+    <hyperlink ref="B19" r:id="rId18" display="http://csharp-video-tutorials.blogspot.com/2012/11/binding-aspnet-dropdownlist-with-xml.html" xr:uid="{F0FA7B94-6337-462A-BBC3-225D45BC9970}"/>
+    <hyperlink ref="B20" r:id="rId19" display="http://csharp-video-tutorials.blogspot.com/2012/11/mapping-virtual-path-to-physical-path.html" xr:uid="{489B940A-7599-45C9-8D3D-DB75F9A929F8}"/>
+    <hyperlink ref="B21" r:id="rId20" display="http://csharp-video-tutorials.blogspot.com/2012/11/mapping-virtual-path-to-physical-path_6.html" xr:uid="{74280026-5642-43FB-A8BD-64CA8891126E}"/>
+    <hyperlink ref="B22" r:id="rId21" display="http://csharp-video-tutorials.blogspot.com/2012/11/retrieving-selected-item-text-value-and.html" xr:uid="{39D8014B-D670-4BFE-B407-51CD8E4BA6F9}"/>
+    <hyperlink ref="B23" r:id="rId22" display="http://csharp-video-tutorials.blogspot.com/2012/11/cascading-dropdown-in-aspnet-part-22.html" xr:uid="{63284B80-7ABC-4C4F-801A-28852EEAFDEE}"/>
+    <hyperlink ref="B24" r:id="rId23" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-checkboxlist-control-part-23.html" xr:uid="{0C2E3E87-AB36-4F49-B9A5-A904600100E5}"/>
+    <hyperlink ref="B25" r:id="rId24" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-checkboxlist-select-or-deselect.html" xr:uid="{F2FBDB3A-B755-4A15-9E74-F86DB08E35B1}"/>
+    <hyperlink ref="B26" r:id="rId25" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-listbox-control-part-25.html" xr:uid="{1CCA6A8B-5E8F-4078-9341-E10E39ADEFA6}"/>
+    <hyperlink ref="B27" r:id="rId26" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-checkboxlist-and-listbox-real.html" xr:uid="{79887583-9F3C-4DA7-9DA1-35E146DB77AE}"/>
+    <hyperlink ref="B28" r:id="rId27" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-radiobuttonlist-control-part-27.html" xr:uid="{CA1B8652-C3B2-4B35-B208-E7985C094E44}"/>
+    <hyperlink ref="B29" r:id="rId28" display="http://csharp-video-tutorials.blogspot.com/2012/11/bulleted-list-in-aspnet-part-28.html" xr:uid="{DC2A13B3-09A1-4311-A002-C1B954727ED0}"/>
+    <hyperlink ref="B30" r:id="rId29" display="http://csharp-video-tutorials.blogspot.com/2012/11/list-controls-in-aspnet-part-29.html" xr:uid="{68DB3CB1-C8A0-429A-BE3A-182EB0128058}"/>
+    <hyperlink ref="B31" r:id="rId30" display="http://csharp-video-tutorials.blogspot.com/2012/11/fileupload-control-in-aspnet-part-30.html" xr:uid="{D4ABDF67-1F9C-4BB1-8DF5-48C8D59B65DA}"/>
+    <hyperlink ref="B32" r:id="rId31" display="http://csharp-video-tutorials.blogspot.com/2012/11/adrotator-control-in-aspnet-part-31.html" xr:uid="{3285EF80-7B81-4104-8B02-127372415921}"/>
+    <hyperlink ref="B33" r:id="rId32" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-calendar-control-part-32.html" xr:uid="{7607213B-B857-48E8-8AF4-752BF88ACB7E}"/>
+    <hyperlink ref="B34" r:id="rId33" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-calendar-control-properties-and.html" xr:uid="{F6891B29-2AC1-4F6D-8A4D-D97F04033804}"/>
+    <hyperlink ref="B35" r:id="rId34" display="http://csharp-video-tutorials.blogspot.com/2012/11/hidden-field-in-aspnet-part-34.html" xr:uid="{AF8B01CC-2380-458D-833C-5DF01144DD4D}"/>
+    <hyperlink ref="B36" r:id="rId35" display="http://csharp-video-tutorials.blogspot.com/2012/11/multiview-control-in-aspnet-part-35.html" xr:uid="{4AAD6E37-0E0A-4E3D-B7AA-45A9FAB425C8}"/>
+    <hyperlink ref="B37" r:id="rId36" display="http://csharp-video-tutorials.blogspot.com/2012/11/wizard-control-in-aspnet-part-36.html" xr:uid="{7150C64D-66C5-4C06-A6E5-87028CA16408}"/>
+    <hyperlink ref="B38" r:id="rId37" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-wizard-control-properties-part-37.html" xr:uid="{E30C1AA7-01FE-4FA2-B909-87D472FD6FD0}"/>
+    <hyperlink ref="B39" r:id="rId38" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-wizard-control-events-part-38.html" xr:uid="{36FEF201-FE47-44E1-92E2-DA840CB64363}"/>
+    <hyperlink ref="B40" r:id="rId39" display="http://csharp-video-tutorials.blogspot.com/2012/11/usesubmitbehavior-property-of-button.html" xr:uid="{04C3ED16-926D-4C10-80C9-AC9AA2CC0B2F}"/>
+    <hyperlink ref="B41" r:id="rId40" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-wizard-control-templates-part-40.html" xr:uid="{5CD1D617-3068-46C2-A321-5B196443D583}"/>
+    <hyperlink ref="B42" r:id="rId41" display="http://csharp-video-tutorials.blogspot.com/2012/11/literal-control-in-aspnet-part-41.html" xr:uid="{4E8CB823-FF08-4D2D-85C0-2706D1BBFE1B}"/>
+    <hyperlink ref="B43" r:id="rId42" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-panel-control-part-42.html" xr:uid="{4BC433C4-30C9-4560-8314-917036C1EA25}"/>
+    <hyperlink ref="B44" r:id="rId43" display="http://csharp-video-tutorials.blogspot.com/2012/11/creating-controls-dynamically-using.html" xr:uid="{912C5E5C-CD52-4156-9FCE-85FDCFBC6606}"/>
+    <hyperlink ref="B45" r:id="rId44" display="http://csharp-video-tutorials.blogspot.com/2012/11/requiredfield-validator-control-in.html" xr:uid="{1B43A418-BF3C-4CB3-8BBB-EB2253905DDC}"/>
+    <hyperlink ref="B46" r:id="rId45" display="http://csharp-video-tutorials.blogspot.com/2012/11/rangevalidator-control-in-aspnet-part-45.html" xr:uid="{1691FACD-FC2F-48C5-9FAD-C396302FA29F}"/>
+    <hyperlink ref="B47" r:id="rId46" display="http://csharp-video-tutorials.blogspot.com/2012/11/comparevalidator-control-in-aspnet-part.html" xr:uid="{2347D4ED-99F1-4B85-8FC1-B18D0245A5C2}"/>
+    <hyperlink ref="B48" r:id="rId47" display="http://csharp-video-tutorials.blogspot.com/2012/11/regularexpressionvalidator-control-in.html" xr:uid="{63F5FAE9-3D60-41B5-B9D7-927C6CBFBF25}"/>
+    <hyperlink ref="B49" r:id="rId48" display="http://csharp-video-tutorials.blogspot.com/2012/11/customvalidator-control-in-aspnet-part.html" xr:uid="{1B355500-4366-40DC-9184-3097314EF0C3}"/>
+    <hyperlink ref="B50" r:id="rId49" display="http://csharp-video-tutorials.blogspot.com/2012/11/validationsummary-control-in-aspnet.html" xr:uid="{FE2DEEEB-E29A-47F2-91E4-9FEDB932BB9D}"/>
+    <hyperlink ref="B51" r:id="rId50" display="http://csharp-video-tutorials.blogspot.com/2012/11/validationgroups-in-aspnet-part-50.html" xr:uid="{7C59873F-49F3-434B-B4FF-C3B62F720344}"/>
+    <hyperlink ref="B52" r:id="rId51" display="http://csharp-video-tutorials.blogspot.com/2012/11/different-page-navigation-techniques-in.html" xr:uid="{72D28495-FEF0-4D2D-93A7-ABB67644BEDB}"/>
+    <hyperlink ref="B53" r:id="rId52" display="http://csharp-video-tutorials.blogspot.com/2012/11/responseredirect-in-aspnet-part-52.html" xr:uid="{48E7D5B4-DBA0-4750-9621-20D6A0828F3D}"/>
+    <hyperlink ref="B54" r:id="rId53" display="http://csharp-video-tutorials.blogspot.com/2012/11/servertransfer-in-aspnet-part-53.html" xr:uid="{4E40BDCA-F893-4583-930C-8B6F7653CAD7}"/>
+    <hyperlink ref="B55" r:id="rId54" display="http://csharp-video-tutorials.blogspot.com/2012/11/serverexecute-in-aspnet-part-54.html" xr:uid="{2393A311-662F-4948-9FD4-F59204EC52F0}"/>
+    <hyperlink ref="B56" r:id="rId55" display="http://csharp-video-tutorials.blogspot.com/2012/11/cross-page-posting-in-aspnet-part-55.html" xr:uid="{496DCD94-6473-4C82-861C-5371922BEA0F}"/>
+    <hyperlink ref="B57" r:id="rId56" display="http://csharp-video-tutorials.blogspot.com/2012/11/cross-page-postback-strongly-typed.html" xr:uid="{D47C18AD-4202-44D6-8EAA-19701387F915}"/>
+    <hyperlink ref="B58" r:id="rId57" display="http://csharp-video-tutorials.blogspot.com/2012/11/opening-new-window-using-javascript-in.html" xr:uid="{FA0BEC5B-1C5D-4315-AD79-5875E27103B4}"/>
+    <hyperlink ref="B59" r:id="rId58" display="http://csharp-video-tutorials.blogspot.com/2012/11/techniques-to-send-data-from-one.html" xr:uid="{EE782C95-F4AA-49DA-8D9F-34C847A0AA26}"/>
+    <hyperlink ref="B60" r:id="rId59" display="http://csharp-video-tutorials.blogspot.com/2012/11/querystring-in-aspnet-part-59.html" xr:uid="{26FC2CF6-87C2-464A-8D69-43735E54DA43}"/>
+    <hyperlink ref="B61" r:id="rId60" display="http://csharp-video-tutorials.blogspot.com/2012/11/cookies-in-aspnet-part-60.html" xr:uid="{66901BA6-3A5F-46F3-9693-63367E55C6CF}"/>
+    <hyperlink ref="B62" r:id="rId61" display="http://csharp-video-tutorials.blogspot.com/2012/11/how-to-check-if-cookies-are-enabled-or.html" xr:uid="{50A04E5D-F498-4A3F-9C06-EB5909C015DB}"/>
+    <hyperlink ref="B63" r:id="rId62" display="http://csharp-video-tutorials.blogspot.com/2012/11/aspnet-session-state-part-62.html" xr:uid="{275C8BF9-6391-40DB-81D1-86B6DE22C16B}"/>
+    <hyperlink ref="B64" r:id="rId63" display="http://csharp-video-tutorials.blogspot.com/2012/11/cookie-less-sessions-in-aspnet-part-63.html" xr:uid="{3BDD26F1-B2D8-4979-9E85-69F9F855E4C9}"/>
+    <hyperlink ref="B65" r:id="rId64" display="http://csharp-video-tutorials.blogspot.com/2012/12/inporc-aspnet-session-state-mode.html" xr:uid="{B93FF197-D097-4ADB-89D9-D6A0DD507D91}"/>
+    <hyperlink ref="B66" r:id="rId65" display="http://csharp-video-tutorials.blogspot.com/2012/12/stateserver-aspnet-session-state-mode.html" xr:uid="{C897E0E3-EE1C-442D-8949-A7F40536C643}"/>
+    <hyperlink ref="B67" r:id="rId66" display="http://csharp-video-tutorials.blogspot.com/2012/12/sqlserver-aspnet-session-state-mode.html" xr:uid="{D7A775AC-FB33-40A1-88C0-8AB46D5F607B}"/>
+    <hyperlink ref="B68" r:id="rId67" display="http://csharp-video-tutorials.blogspot.com/2012/12/aspnet-application-state-part-67.html" xr:uid="{4D642667-5146-47DC-A79D-9258350AE03C}"/>
+    <hyperlink ref="B69" r:id="rId68" display="http://csharp-video-tutorials.blogspot.com/2012/12/aspnet-application-state-real-time.html" xr:uid="{FBF17DBC-2172-4359-9C1F-8A2E64716769}"/>
+    <hyperlink ref="B70" r:id="rId69" display="http://csharp-video-tutorials.blogspot.com/2012/12/exception-handling-in-aspnet-part-69.html" xr:uid="{712AACC3-D022-4AB7-BDCA-C380E3D12790}"/>
+    <hyperlink ref="B71" r:id="rId70" display="http://csharp-video-tutorials.blogspot.com/2012/12/error-events-in-aspnet-part-70.html" xr:uid="{3EB571E0-475C-4755-A1A0-C8A4E4FA9A31}"/>
+    <hyperlink ref="B72" r:id="rId71" display="http://csharp-video-tutorials.blogspot.com/2012/12/custom-errors-in-aspnet-part-71.html" xr:uid="{087BA534-8E66-4F19-82B4-D8653486229D}"/>
+    <hyperlink ref="B73" r:id="rId72" display="http://csharp-video-tutorials.blogspot.com/2012/12/windows-event-viewer-part-72.html" xr:uid="{D65206C0-B15E-4CEE-87E0-47F21D1C72A5}"/>
+    <hyperlink ref="B74" r:id="rId73" display="http://csharp-video-tutorials.blogspot.com/2012/12/logging-exceptions-to-windows.html" xr:uid="{88B23F85-1CA7-433D-9CCB-0C7461FE2708}"/>
+    <hyperlink ref="B75" r:id="rId74" display="http://csharp-video-tutorials.blogspot.com/2012/12/logging-exceptions-as-information-entry.html" xr:uid="{A9F812C5-6C53-49B4-B618-55DFB7E439C4}"/>
+    <hyperlink ref="B76" r:id="rId75" display="http://csharp-video-tutorials.blogspot.com/2012/12/logging-exception-to-database-part-75.html" xr:uid="{91BC0319-F249-4994-B77F-E0F33EDEB461}"/>
+    <hyperlink ref="B77" r:id="rId76" display="http://csharp-video-tutorials.blogspot.com/2012/12/customizing-aspnet-exception-logging.html" xr:uid="{96FDA438-06C1-4B54-9A57-B36FB10FB976}"/>
+    <hyperlink ref="B78" r:id="rId77" display="http://csharp-video-tutorials.blogspot.com/2012/12/sending-emails-using-aspnet-part-77.html" xr:uid="{3B84DEC3-DCEE-4547-ABE1-86687D9472A5}"/>
+    <hyperlink ref="B79" r:id="rId78" display="http://csharp-video-tutorials.blogspot.com/2012/12/sending-emails-in-aspnet-using-smtp.html" xr:uid="{A7E4E1C7-8AD4-48E6-BF6F-E90C4F8A00D7}"/>
+    <hyperlink ref="B80" r:id="rId79" display="http://csharp-video-tutorials.blogspot.com/2012/12/tracing-in-aspnet-part-79.html" xr:uid="{FDE903DA-1C71-4181-8598-9A5C6178AA18}"/>
+    <hyperlink ref="B81" r:id="rId80" display="http://csharp-video-tutorials.blogspot.com/2012/12/writing-custom-aspnet-tracing-messages.html" xr:uid="{6FD5BEEC-772C-45B2-B613-022EAA4E29F7}"/>
+    <hyperlink ref="B82" r:id="rId81" display="http://csharp-video-tutorials.blogspot.com/2012/12/tracing-in-aspnet-real-time-example.html" xr:uid="{E6CBA1CE-8C8F-43BA-90D6-CADD3040BE8F}"/>
+    <hyperlink ref="B83" r:id="rId82" display="http://csharp-video-tutorials.blogspot.com/2012/12/application-pools-in-iis-part-82.html" xr:uid="{C35E0C79-07F3-41DF-9643-1A4A245E85EB}"/>
+    <hyperlink ref="B84" r:id="rId83" display="http://csharp-video-tutorials.blogspot.com/2012/12/applications-isolation-using.html" xr:uid="{C7F02DB1-35B4-4EAF-8DCA-39B443742EEB}"/>
+    <hyperlink ref="B85" r:id="rId84" display="http://csharp-video-tutorials.blogspot.com/2012/12/application-pools-in-iis-security-part.html" xr:uid="{F0A43382-B16B-4EE3-9127-0CD01A8812CD}"/>
+    <hyperlink ref="B86" r:id="rId85" display="http://csharp-video-tutorials.blogspot.com/2012/12/anonymous-authentication-in-aspnet-part.html" xr:uid="{38E5D37C-5463-4B8E-9F21-3AD9D8B5C744}"/>
+    <hyperlink ref="B87" r:id="rId86" display="http://csharp-video-tutorials.blogspot.com/2012/12/anonymous-authentication-and-aspnet.html" xr:uid="{16A66D39-BE1A-475C-B206-8B0489A7CA4D}"/>
+    <hyperlink ref="B88" r:id="rId87" display="http://csharp-video-tutorials.blogspot.com/2012/12/windows-authentication-in-aspnet-part-87.html" xr:uid="{89E5478E-06CD-4EE7-8FE5-914C50B59D98}"/>
+    <hyperlink ref="B89" r:id="rId88" display="http://csharp-video-tutorials.blogspot.com/2012/12/windows-authentication-and.html" xr:uid="{1F8C2A04-0439-4E31-BFC9-340103273E5B}"/>
+    <hyperlink ref="B90" r:id="rId89" display="http://csharp-video-tutorials.blogspot.com/2012/12/windows-authentication-and-folder-level.html" xr:uid="{3565EC86-4464-4585-B6E0-993ED2CB95D4}"/>
+    <hyperlink ref="B91" r:id="rId90" display="http://csharp-video-tutorials.blogspot.com/2012/12/forms-authentication-using-user-names.html" xr:uid="{38BEC677-8E87-49D6-A522-B655DFF90633}"/>
+    <hyperlink ref="B92" r:id="rId91" display="http://csharp-video-tutorials.blogspot.com/2012/12/forms-authentication-in-aspnet-and-user.html" xr:uid="{B3DE8C93-09B8-4F95-8C0C-3667B021B211}"/>
+    <hyperlink ref="B93" r:id="rId92" display="http://csharp-video-tutorials.blogspot.com/2012/12/forms-authentication-against-users-in.html" xr:uid="{2D14526A-1697-4BB9-AC8A-AF9E01D72A2B}"/>
+    <hyperlink ref="B94" r:id="rId93" display="http://csharp-video-tutorials.blogspot.com/2012/12/forms-authentication-and-locking-user.html" xr:uid="{85987681-9495-4724-BE2C-393AB2ADE9E7}"/>
+    <hyperlink ref="B95" r:id="rId94" display="http://csharp-video-tutorials.blogspot.com/2012/12/unlocking-locked-user-accounts-part-94.html" xr:uid="{91950CB4-900E-41BF-8C11-F340E65D0444}"/>
+    <hyperlink ref="B96" r:id="rId95" display="http://csharp-video-tutorials.blogspot.com/2012/12/implementing-password-reset-link-in.html" xr:uid="{6ADFE8CF-1CBB-4055-ADB6-379A6EEE7BD7}"/>
+    <hyperlink ref="B97" r:id="rId96" display="http://csharp-video-tutorials.blogspot.com/2012/12/implementing-change-password-page-in.html" xr:uid="{A9EA6395-D894-4355-B1E2-5F7839EBA59F}"/>
+    <hyperlink ref="B98" r:id="rId97" display="http://csharp-video-tutorials.blogspot.com/2012/12/changing-password-by-providing-current.html" xr:uid="{BA4FCC61-6E42-4878-BC09-2CEBBAA2036E}"/>
+    <hyperlink ref="B99" r:id="rId98" display="http://csharp-video-tutorials.blogspot.com/2012/12/unlocking-locked-user-accounts-using.html" xr:uid="{E7D4AB4A-2509-4F87-8A54-E49B0A1F80BC}"/>
+    <hyperlink ref="B100" r:id="rId99" display="http://csharp-video-tutorials.blogspot.com/2012/12/implementing-enable-button-to-unlock.html" xr:uid="{B3858AD9-07C0-4F7B-AFCC-3AE437766CF5}"/>
+    <hyperlink ref="B101" r:id="rId100" display="http://csharp-video-tutorials.blogspot.com/2012/12/secure-socket-layer-in-aspnet-part-100.html" xr:uid="{07849E47-09DE-46F0-B06E-1D6B6A57CFF8}"/>
+    <hyperlink ref="B102" r:id="rId101" display="http://csharp-video-tutorials.blogspot.com/2012/12/implementing-ssl-in-aspnet-web.html" xr:uid="{F66CC27D-9D58-475B-A272-B3CE0A7DEC1D}"/>
+    <hyperlink ref="B103" r:id="rId102" display="http://csharp-video-tutorials.blogspot.com/2012/12/redirect-http-to-https-in-iis-part-102.html" xr:uid="{C6F97986-7014-4482-9179-BCE573DAFE98}"/>
+    <hyperlink ref="B104" r:id="rId103" display="http://csharp-video-tutorials.blogspot.com/2012/12/redirect-http-to-https-in-iis-using.html" xr:uid="{8F38241C-FF4C-40AB-BE1E-C08DA4E1FE5D}"/>
+    <hyperlink ref="B105" r:id="rId104" display="http://csharp-video-tutorials.blogspot.com/2012/12/user-controls-in-aspnet-part-104.html" xr:uid="{38D4B1E9-7A30-448C-9E9F-A5EBC97CDD45}"/>
+    <hyperlink ref="B106" r:id="rId105" display="http://csharp-video-tutorials.blogspot.com/2012/12/adding-and-using-user-controls-on.html" xr:uid="{A3ED794E-6EA3-471D-A0B1-52F6F43FFDB2}"/>
+    <hyperlink ref="B107" r:id="rId106" display="http://csharp-video-tutorials.blogspot.com/2013/01/raising-custom-events-from-user.html" xr:uid="{AB98CAE4-96BF-4E52-9494-63160B9C884C}"/>
+    <hyperlink ref="B108" r:id="rId107" display="http://csharp-video-tutorials.blogspot.com/2013/01/consuming-user-control-custom-events.html" xr:uid="{7D6EDB1E-9849-42E9-9513-D459E21D2173}"/>
+    <hyperlink ref="B109" r:id="rId108" display="http://csharp-video-tutorials.blogspot.com/2013/01/events-and-delegates-in-c-part-108.html" xr:uid="{B3656B63-DDA8-4368-A32C-FBB4E9442F18}"/>
+    <hyperlink ref="B110" r:id="rId109" display="http://csharp-video-tutorials.blogspot.com/2013/01/loading-user-controls-dynamically-part.html" xr:uid="{FAF36E1B-2E11-46B4-9EA3-2AF90273A3AF}"/>
+    <hyperlink ref="B111" r:id="rId110" display="http://csharp-video-tutorials.blogspot.com/2013/01/loading-controls-dynamically-in-aspnet.html" xr:uid="{0A69A7D1-352E-4733-B6D4-2F9240CC9117}"/>
+    <hyperlink ref="B112" r:id="rId111" display="http://csharp-video-tutorials.blogspot.com/2013/01/navigating-to-specific-month-and-year.html" xr:uid="{D82BA7C7-0DC2-40F3-956A-238F6AD2861D}"/>
+    <hyperlink ref="B113" r:id="rId112" display="http://csharp-video-tutorials.blogspot.com/2013/01/aspnet-custom-server-controls-part-112.html" xr:uid="{05027AB7-E76A-4D37-AC05-4CA9D6FA760E}"/>
+    <hyperlink ref="B114" r:id="rId113" display="http://csharp-video-tutorials.blogspot.com/2013/01/adding-composite-custom-controls-to.html" xr:uid="{ADA27EB6-D098-4415-AA01-D50E54FF7A5A}"/>
+    <hyperlink ref="B115" r:id="rId114" display="http://csharp-video-tutorials.blogspot.com/2013/01/adding-properties-to-composite-custom.html" xr:uid="{686C199C-853C-4017-8F4F-CC484224F3C5}"/>
+    <hyperlink ref="B116" r:id="rId115" display="http://csharp-video-tutorials.blogspot.com/2013/01/solving-problems-of-aspnet-composite.html" xr:uid="{8FD6C95D-7830-455D-80B3-5C8A133565B5}"/>
+    <hyperlink ref="B117" r:id="rId116" display="http://csharp-video-tutorials.blogspot.com/2013/01/adding-custom-events-to-aspnet.html" xr:uid="{204A3C2C-833F-4E21-8572-48BE8ACC2D50}"/>
+    <hyperlink ref="B118" r:id="rId117" display="http://csharp-video-tutorials.blogspot.com/2013/01/assigning-image-to-composite-custom.html" xr:uid="{8E2AB042-AF69-4F0A-96E5-75996AD7C5E1}"/>
+    <hyperlink ref="B119" r:id="rId118" display="http://csharp-video-tutorials.blogspot.com/2013/01/difference-between-user-controls-and.html" xr:uid="{579F2277-4E81-452C-9EA1-3D506F4C56E7}"/>
+    <hyperlink ref="B120" r:id="rId119" display="http://csharp-video-tutorials.blogspot.com/2013/01/caching-in-aspnet-part-119.html" xr:uid="{4FA12C35-C068-491D-873F-4DB0B2A1BB39}"/>
+    <hyperlink ref="B121" r:id="rId120" display="http://csharp-video-tutorials.blogspot.com/2013/01/caching-multiple-responses-for-single.html" xr:uid="{4E682012-5E0E-419D-A4B8-708758BE8C11}"/>
+    <hyperlink ref="B122" r:id="rId121" display="http://csharp-video-tutorials.blogspot.com/2013/01/controlling-aspnet-caching-in-code-part.html" xr:uid="{42999654-CF89-4E65-B4B7-26F0636E2D38}"/>
+    <hyperlink ref="B123" r:id="rId122" display="http://csharp-video-tutorials.blogspot.com/2013/01/fragment-caching-in-aspnet-part-122.html" xr:uid="{FB369CD9-739F-42BE-BA57-A1FDC0D11227}"/>
+    <hyperlink ref="B124" r:id="rId123" display="http://csharp-video-tutorials.blogspot.com/2013/02/web-form-caching-based-on-get-and-post.html" xr:uid="{D575D486-E893-482C-9418-F8F4A71D9AB8}"/>
+    <hyperlink ref="B125" r:id="rId124" display="http://csharp-video-tutorials.blogspot.com/2013/02/caching-multiple-versions-of-user.html" xr:uid="{5A78EF44-031B-4595-9720-204C5C5D4D9F}"/>
+    <hyperlink ref="B126" r:id="rId125" display="http://csharp-video-tutorials.blogspot.com/2013/02/caching-multiple-versions-of-user_6.html" xr:uid="{A1897637-8200-487B-8910-4355449DCEE5}"/>
+    <hyperlink ref="B127" r:id="rId126" display="http://csharp-video-tutorials.blogspot.com/2013/02/caching-application-data-in-aspnet-part.html" xr:uid="{AF5BAEBC-8BE3-47BF-B093-30C695855564}"/>
+    <hyperlink ref="B128" r:id="rId127" display="http://csharp-video-tutorials.blogspot.com/2013/02/different-ways-to-cache-application.html" xr:uid="{DDC18639-D5B2-400E-B9A7-D6D6F661FACE}"/>
+    <hyperlink ref="B129" r:id="rId128" display="http://csharp-video-tutorials.blogspot.com/2013/02/caching-in-aspnet-absoluteexpiration.html" xr:uid="{ABCB2C7F-1AD8-4F6D-A64C-EDC3FC311E14}"/>
+    <hyperlink ref="B130" r:id="rId129" display="http://csharp-video-tutorials.blogspot.com/2013/02/cache-dependency-on-files-in-aspnet.html" xr:uid="{14116FDB-F993-4B26-982E-F15374E4EF69}"/>
+    <hyperlink ref="B131" r:id="rId130" display="http://csharp-video-tutorials.blogspot.com/2013/02/reloading-or-refreshing-cache.html" xr:uid="{D4D05B54-B186-4241-A89F-60A3DA5A7357}"/>
+    <hyperlink ref="B132" r:id="rId131" display="http://csharp-video-tutorials.blogspot.com/2013/02/cache-dependency-on-sql-server-database.html" xr:uid="{57CABBDA-1720-44F2-BF7B-EB02B8433E76}"/>
+    <hyperlink ref="B133" r:id="rId132" display="http://csharp-video-tutorials.blogspot.com/2013/02/reload-data-into-cache-automatically.html" xr:uid="{03800494-3BD7-4A71-BE5F-43F1419EF823}"/>
+    <hyperlink ref="B134" r:id="rId133" display="http://csharp-video-tutorials.blogspot.com/2013/03/what-is-autoeventwireup-in-aspnet-part.html" xr:uid="{2C4752A4-F283-4F16-800D-94E705EDE417}"/>
+    <hyperlink ref="B135" r:id="rId134" display="http://csharp-video-tutorials.blogspot.com/2013/07/add-image-slideshow-to-your-website.html" xr:uid="{D26F2C1D-A366-494D-AF07-90B623B7E9DD}"/>
+    <hyperlink ref="B136" r:id="rId135" display="http://csharp-video-tutorials.blogspot.com/2013/07/display-images-in-sequence-in-image.html" xr:uid="{CE7FEAE1-7312-44C8-BCA6-BF775BF4A0C8}"/>
+    <hyperlink ref="B137" r:id="rId136" display="http://csharp-video-tutorials.blogspot.com/2013/07/part-136-provide-capability-to-start.html" xr:uid="{9F47F75C-9705-4A9A-B936-9BCDC5A34956}"/>
+    <hyperlink ref="B138" r:id="rId137" display="http://csharp-video-tutorials.blogspot.com/2013/07/add-images-to-slideshow-using-xml-file.html" xr:uid="{15345C7A-709E-4E3D-813F-E6392AEE7C79}"/>
+    <hyperlink ref="B139" r:id="rId138" display="http://csharp-video-tutorials.blogspot.com/2013/07/add-images-to-slideshow-using-database.html" xr:uid="{C9D3CA7B-59B2-482E-A913-877A56E889E8}"/>
+    <hyperlink ref="B140" r:id="rId139" display="http://csharp-video-tutorials.blogspot.com/2013/08/how-to-upload-and-download-files-using.html" xr:uid="{59AF3F81-14BC-40E6-BC13-F01B50393BDF}"/>
+    <hyperlink ref="B141" r:id="rId140" display="http://csharp-video-tutorials.blogspot.com/2013/08/part-140-creating-image-gallery-using.html" xr:uid="{51B67993-4270-46DB-9EB7-8C5C1262D5FC}"/>
+    <hyperlink ref="B142" r:id="rId141" display="http://csharp-video-tutorials.blogspot.com/2013/08/part-141-contact-us-page-using-aspnet.html" xr:uid="{9DC28454-6798-4FBD-938A-C9D21B5E4634}"/>
+    <hyperlink ref="B143" r:id="rId142" display="http://csharp-video-tutorials.blogspot.com/2013/08/part-142-contact-us-page-using-aspnet.html" xr:uid="{264B1DA1-A486-4C2B-BE03-E097418BF5E8}"/>
+    <hyperlink ref="B144" r:id="rId143" display="http://csharp-video-tutorials.blogspot.com/2013/09/part-143-difference-between-http-get.html" xr:uid="{08643D4C-0414-42E5-AA70-8EE0316D6F72}"/>
+    <hyperlink ref="B145" r:id="rId144" display="http://csharp-video-tutorials.blogspot.com/2013/09/part-144-how-to-check-if-request-method.html" xr:uid="{DA861061-81CB-448B-A292-02482CDF40D9}"/>
+    <hyperlink ref="B146" r:id="rId145" display="http://csharp-video-tutorials.blogspot.com/2013/09/part-145-implementing-autocomplete.html" xr:uid="{32753840-C275-49E6-83A9-13B3A7007C57}"/>
+    <hyperlink ref="B147" r:id="rId146" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-146-why-use-master-pages-in-aspnet.html" xr:uid="{A0D729E0-8D33-474F-BC68-B7A9D2349B27}"/>
+    <hyperlink ref="B148" r:id="rId147" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-147-master-pages-in-aspnet.html" xr:uid="{C27E9996-2423-41AD-AF1E-D24E6FE5EDE9}"/>
+    <hyperlink ref="B149" r:id="rId148" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-148-passing-data-from-content-page.html" xr:uid="{D2A7C01B-B515-4DD7-B62B-9B5CC911B4B4}"/>
+    <hyperlink ref="B150" r:id="rId149" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-149-passing-data-from-master-page.html" xr:uid="{76A4A4A5-FFDE-42FE-9711-B66BE581556B}"/>
+    <hyperlink ref="B151" r:id="rId150" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-150-default-content-in.html" xr:uid="{9EA617E5-D9AB-4C66-AA93-071DDF120F4D}"/>
+    <hyperlink ref="B152" r:id="rId151" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-151-assigning-master-page.html" xr:uid="{D2D95CBB-DB53-433D-89F2-5FB744FEDCAA}"/>
+    <hyperlink ref="B153" r:id="rId152" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-152-master-page-content-page-user.html" xr:uid="{74EAA126-221F-4F22-8DD2-82B146E6773C}"/>
+    <hyperlink ref="B154" r:id="rId153" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-153-menu-control-in-aspnet.html" xr:uid="{387B4826-4318-4261-A5C9-B4A88C4C9220}"/>
+    <hyperlink ref="B155" r:id="rId154" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-154-using-styles-with-aspnet-menu.html" xr:uid="{AB137DD1-16BD-4F85-85BF-BBB7308C27BF}"/>
+    <hyperlink ref="B156" r:id="rId155" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-155-binding-aspnet-menu-control-to.html" xr:uid="{9970E837-76C0-48F9-B693-3173DD64EC31}"/>
+    <hyperlink ref="B157" r:id="rId156" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-156-binding-aspnet-menu-control-to.html" xr:uid="{D7B0BAFB-D79F-4555-AF74-C3A58C020A2B}"/>
+    <hyperlink ref="B158" r:id="rId157" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-157-sitemappath-control-in-aspnet.html" xr:uid="{0A953234-A305-4212-8852-E42F6F5C3669}"/>
+    <hyperlink ref="B159" r:id="rId158" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-158-binding-aspnet-menu-control-to.html" xr:uid="{0DDFB775-27C6-45CF-B5CE-2CABAD01DCE4}"/>
+    <hyperlink ref="B160" r:id="rId159" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-159-treeview-control-in-aspnet.html" xr:uid="{4DA42C14-974D-4A95-A126-E37871E8F441}"/>
+    <hyperlink ref="B161" r:id="rId160" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-160-binding-aspnet-treeview.html" xr:uid="{AB76BA4A-8385-4B29-B1F0-41F32DFBB621}"/>
+    <hyperlink ref="B162" r:id="rId161" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-161-binding-treeview-control-to.html" xr:uid="{BFA10A4B-85E9-4399-BE6F-C03CF08198B9}"/>
+    <hyperlink ref="B163" r:id="rId162" display="http://csharp-video-tutorials.blogspot.com/2013/10/part-162-binding-aspnet-treeview.html" xr:uid="{DA1E00EE-F913-4BC1-BEDA-F80F16281B17}"/>
+    <hyperlink ref="B164" r:id="rId163" display="http://csharp-video-tutorials.blogspot.com/2013/11/part-163-dynamically-adding-treenodes.html" xr:uid="{85A481E4-7B4D-48D6-AEAC-B3294BC64B23}"/>
+    <hyperlink ref="B165" r:id="rId164" display="http://csharp-video-tutorials.blogspot.com/2013/11/part-164-displaying-organization.html" xr:uid="{8FE68277-4979-48C5-A987-02A7CB581A66}"/>
+    <hyperlink ref="B166" r:id="rId165" display="http://csharp-video-tutorials.blogspot.com/2014/10/part-165-how-to-display-icon-for.html" xr:uid="{B22FDD3E-0468-410F-A7EE-327F399109BB}"/>
+    <hyperlink ref="B167" r:id="rId166" display="http://csharp-video-tutorials.blogspot.com/2014/10/captcha-control-in-aspnet.html" xr:uid="{A9E22490-6A14-407C-9D0C-7FB9B28D272B}"/>
+    <hyperlink ref="B168" r:id="rId167" display="http://csharp-video-tutorials.blogspot.com/2014/10/using-aspnet-validation-controls-with.html" xr:uid="{65216575-0585-4F62-8D7A-37D980500A3D}"/>
+    <hyperlink ref="B169" r:id="rId168" display="http://csharp-video-tutorials.blogspot.com/2014/10/customizing-recaptcha-control_12.html" xr:uid="{AD936313-41BF-445F-AB36-754DFB395011}"/>
+    <hyperlink ref="B170" r:id="rId169" display="http://csharp-video-tutorials.blogspot.com/2015/08/save-image-to-database-using-aspnet.html" xr:uid="{EB3C1E29-1401-4104-B1D2-925D3E73EC2D}"/>
+    <hyperlink ref="B171" r:id="rId170" display="http://csharp-video-tutorials.blogspot.com/2015/08/load-image-from-database-in-aspnet.html" xr:uid="{AD0BA8FA-8B89-45CD-9E29-4DB98959FC6F}"/>
+    <hyperlink ref="B172" r:id="rId171" display="http://csharp-video-tutorials.blogspot.com/2015/08/how-to-show-images-from-database-in.html" xr:uid="{80DE80B9-AD85-44EE-9887-CC5F890D1C0D}"/>
+    <hyperlink ref="B173" r:id="rId172" display="http://csharp-video-tutorials.blogspot.com/2016/11/display-data-from-two-or-more-database.html" xr:uid="{0B5F9C5E-8062-4B29-91CB-8629CFCE3281}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE41982C-1132-41D5-9211-057F313D7EFA}">
+  <dimension ref="B2:B124"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="7"/>
+    </row>
+    <row r="5" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="17" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="18" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="18" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B106" s="2"/>
+    </row>
+    <row r="107" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B107" s="2"/>
+    </row>
+    <row r="108" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B108" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B109" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B110" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B111" s="2"/>
+    </row>
+    <row r="112" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B112" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B113" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B114" s="2"/>
+    </row>
+    <row r="115" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B115" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B116" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B117" s="2"/>
+    </row>
+    <row r="118" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B118" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B119" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B120" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B121" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B122" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B123" s="2"/>
+    </row>
+    <row r="124" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B124" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{70DF66AD-5787-4E11-9374-AB9CDE2D5B0E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37854B17-4188-42B2-B060-5AA819C27391}">
+  <dimension ref="B2:B18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB4D781-2B23-462F-9FBA-3F11CEE54BC8}">
+  <dimension ref="B1:B60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B59" s="2"/>
+    </row>
+    <row r="60" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9BCAC6-FB98-42EC-80E0-9F343FB2C353}">
+  <dimension ref="B2:B215"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="19" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="1"/>
+    </row>
+    <row r="34" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="1"/>
+    </row>
+    <row r="49" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="1"/>
+    </row>
+    <row r="53" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B57" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B58" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B59" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="1"/>
+    </row>
+    <row r="61" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B63" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="1"/>
+    </row>
+    <row r="65" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="1"/>
+    </row>
+    <row r="69" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B69" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B71" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B73" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B74" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B75" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="1"/>
+    </row>
+    <row r="77" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B77" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B78" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B79" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="1"/>
+    </row>
+    <row r="81" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B81" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B82" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B83" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B84" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B85" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="1"/>
+    </row>
+    <row r="87" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B87" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B90" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B91" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B92" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B93" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="1"/>
+    </row>
+    <row r="95" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B95" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B96" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B98" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B99" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B100" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B101" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B143" s="19" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B159" s="2"/>
+    </row>
+    <row r="160" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B160" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B172" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B197" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B203" s="2"/>
+    </row>
+    <row r="204" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B204" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B215" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:B273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8825,541 +11052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37854B17-4188-42B2-B060-5AA819C27391}">
-  <dimension ref="B2:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB4D781-2B23-462F-9FBA-3F11CEE54BC8}">
-  <dimension ref="B1:B60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="2"/>
-    </row>
-    <row r="60" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9BCAC6-FB98-42EC-80E0-9F343FB2C353}">
-  <dimension ref="B2:B215"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="1"/>
-    </row>
-    <row r="53" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" s="1"/>
-    </row>
-    <row r="57" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="1"/>
-    </row>
-    <row r="61" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="1"/>
-    </row>
-    <row r="65" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" s="1"/>
-    </row>
-    <row r="69" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B71" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72" s="1"/>
-    </row>
-    <row r="73" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B73" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B75" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" s="1"/>
-    </row>
-    <row r="77" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B77" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80" s="1"/>
-    </row>
-    <row r="81" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B81" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B82" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B83" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B84" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B85" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B86" s="1"/>
-    </row>
-    <row r="87" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B90" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B91" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B92" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B93" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B94" s="1"/>
-    </row>
-    <row r="95" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B95" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B98" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B99" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B100" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B101" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="143" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B143" s="19" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="159" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B159" s="2"/>
-    </row>
-    <row r="160" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B160" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B172" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B197" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="203" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B203" s="2"/>
-    </row>
-    <row r="204" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B204" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="215" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B215" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19DA95B5-F9AB-4B81-BCCC-FAC46ABDE61E}">
   <dimension ref="B2:B220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9683,7 +11376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2BB5F3-6D73-4EAE-861F-066485BB1794}">
   <dimension ref="B2:B139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10014,7 +11707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F620628C-FCF2-40EA-A5FD-A98BDA806E86}">
   <dimension ref="B3:B117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10123,7 +11816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{112E3806-5969-4409-95E1-136C6D0E25CA}">
   <dimension ref="B3:B131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10316,7 +12009,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24F10BD0-C34C-4015-B395-16BAFE3467C7}">
   <dimension ref="B2:B251"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10965,7 +12658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35ABDC8A-E025-4503-9367-F8C8800C5D64}">
   <dimension ref="B2:B123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11025,7 +12718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2CB3B2E-077E-45D3-B954-9F826E08BEFB}">
   <dimension ref="B2:B59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11073,129 +12766,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE41982C-1132-41D5-9211-057F313D7EFA}">
-  <dimension ref="B2:B124"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="7"/>
-    </row>
-    <row r="5" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="18" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="18" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B106" s="2"/>
-    </row>
-    <row r="107" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B107" s="2"/>
-    </row>
-    <row r="108" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B108" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B109" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="110" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B110" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B111" s="2"/>
-    </row>
-    <row r="112" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B112" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B113" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B114" s="2"/>
-    </row>
-    <row r="115" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B115" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B116" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="117" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B117" s="2"/>
-    </row>
-    <row r="118" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B118" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="119" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B119" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B120" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="121" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B121" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B122" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B123" s="2"/>
-    </row>
-    <row r="124" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B124" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{70DF66AD-5787-4E11-9374-AB9CDE2D5B0E}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
+++ b/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\WebAppCoding\WebAppCoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8A7114-E6F3-48FC-A541-93BCE23E759B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A8383D-BF9F-4D27-8671-3CFEF9F17675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3031,7 +3031,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3159,6 +3159,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3181,7 +3198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3239,6 +3256,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -8673,7 +8694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29D76A65-EE41-415B-A99C-810B3C929668}">
-  <dimension ref="B2:B173"/>
+  <dimension ref="A2:B173"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -8755,82 +8776,85 @@
         <v>373</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="20" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="22" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="20" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="20" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" s="20" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" s="20" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" s="20" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23" s="20" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B25" s="20" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" s="20" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" s="20" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" s="20" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" s="20" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" s="20" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" s="20" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
         <v>389</v>
       </c>
@@ -9716,6 +9740,7 @@
     <hyperlink ref="B173" r:id="rId172" display="http://csharp-video-tutorials.blogspot.com/2016/11/display-data-from-two-or-more-database.html" xr:uid="{0B5F9C5E-8062-4B29-91CB-8629CFCE3281}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId173"/>
 </worksheet>
 </file>
 

--- a/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
+++ b/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\WebAppCoding\WebAppCoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A8383D-BF9F-4D27-8671-3CFEF9F17675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C4436D-CCEA-47B7-A4C2-855FD54A54A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chapter" sheetId="13" r:id="rId1"/>
@@ -26,6 +26,9 @@
     <sheet name="20" sheetId="10" r:id="rId11"/>
     <sheet name="21" sheetId="11" r:id="rId12"/>
     <sheet name="22" sheetId="12" r:id="rId13"/>
+    <sheet name="37" sheetId="14" r:id="rId14"/>
+    <sheet name="38" sheetId="15" r:id="rId15"/>
+    <sheet name="Sheet3" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="541">
   <si>
     <t>10 .Text Box</t>
   </si>
@@ -3025,6 +3028,36 @@
   </si>
   <si>
     <t>172. Display data from two or more database table columns in asp.net dropdownlist</t>
+  </si>
+  <si>
+    <t>37. Wizard Control</t>
+  </si>
+  <si>
+    <t>Wizard is 0 index properties</t>
+  </si>
+  <si>
+    <t>Activate cancel button</t>
+  </si>
+  <si>
+    <t>Navigate cancel button using url</t>
+  </si>
+  <si>
+    <t>For  this button type- image , cancel page destination url – www.youtube.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancel button text --- </t>
+  </si>
+  <si>
+    <t>Set header</t>
+  </si>
+  <si>
+    <t>Render header according to step</t>
+  </si>
+  <si>
+    <t>38. Wizard Control Event</t>
+  </si>
+  <si>
+    <t>Activate index changed index</t>
   </si>
 </sst>
 </file>
@@ -3198,7 +3231,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3262,6 +3295,9 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4832,6 +4868,788 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>319405</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>179705</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{889A6332-AB56-0767-671E-81CFA89E7B2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="33908" r="22804" b="9426"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="581025"/>
+          <a:ext cx="4586605" cy="1894205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>378246</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94F22ECC-DC48-D08D-3172-445B6082B88F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="3257550"/>
+          <a:ext cx="10741446" cy="1619250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>41113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC0DB0F7-DEAA-D6E4-5173-0A580B4C4DB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609599" y="5934075"/>
+          <a:ext cx="9458325" cy="3089113"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CBCDAE8-A4AE-18FB-C424-3411E7CF9D53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="271" t="8791" r="-271" b="33333"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="9553575"/>
+          <a:ext cx="2698750" cy="1155700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08577A14-C7E8-B0B7-FA44-2504EB1545F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="12049125"/>
+          <a:ext cx="5943600" cy="1943100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>116840</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>78105</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6245E29B-C9F2-F894-4E65-BCFC4EA01E5A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="23168"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="14144625"/>
+          <a:ext cx="3774440" cy="1221105"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>456565</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D68EBAB4-34BA-BDDB-5F5D-D9F52605DF24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="20897"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="16059150"/>
+          <a:ext cx="4723765" cy="1038225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>531495</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>27305</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9338A8E3-210C-6192-3F85-3C8D9C53EEF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="17973675"/>
+          <a:ext cx="4798695" cy="3837305"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>115570</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>27305</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB46098E-0083-9204-7CCA-6368A7571A28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="5525"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="22164675"/>
+          <a:ext cx="3773170" cy="1170305"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>550545</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>71120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A0ACCF6-03BA-ADA4-DF06-CBB2020509CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="18914"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="23688675"/>
+          <a:ext cx="4208145" cy="1023620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>540385</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83FC03E4-7821-BD3D-0C18-9B19C8769216}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="12815"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="25022175"/>
+          <a:ext cx="4197985" cy="994410"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>317478</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84108A70-8735-67AB-5AD9-94DF9738A9E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609599" y="581025"/>
+          <a:ext cx="10680679" cy="1371600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>11088</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F64FC17-3BE5-EDF9-E54B-9CBDB83A516B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="2686050"/>
+          <a:ext cx="7086600" cy="2297088"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3" descr="localhost:44378/WizardEvent - Google Chrome">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DCAF989-5E07-4ACF-736B-468DC99CC92E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="6305" r="54461" b="54938"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="5543550"/>
+          <a:ext cx="4467225" cy="2004060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -10403,6 +11221,90 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C7503C0-8239-401F-824D-F448B1640AB9}">
+  <dimension ref="B2:B92"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="23" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="17" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B83" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B92" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B61" r:id="rId1" display="http://www.youtube.com/" xr:uid="{DB8965D4-C93F-47CF-968F-784AEABD3AC4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75D0CE2-412A-4E45-A15E-28AE503ECBC8}">
+  <dimension ref="B2:B12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63083E52-DF5D-4B9F-8D87-DDB84A984543}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:B273"/>

--- a/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
+++ b/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\WebAppCoding\WebAppCoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C4436D-CCEA-47B7-A4C2-855FD54A54A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE4B691-D957-4E1C-9C1F-BADC6A5AE69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chapter" sheetId="13" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="22" sheetId="12" r:id="rId13"/>
     <sheet name="37" sheetId="14" r:id="rId14"/>
     <sheet name="38" sheetId="15" r:id="rId15"/>
-    <sheet name="Sheet3" sheetId="16" r:id="rId16"/>
+    <sheet name="170" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="550">
   <si>
     <t>10 .Text Box</t>
   </si>
@@ -3059,12 +3059,507 @@
   <si>
     <t>Activate index changed index</t>
   </si>
+  <si>
+    <r>
+      <t>public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>partial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Wizard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> : System.Web.UI.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>protected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page_Load</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>sender</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>EventArgs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>protected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page_PreRender</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>sender</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>EventArgs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8F08C4"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (Wizard1.ActiveStepIndex == 0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            Wizard1.HeaderText = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Personal Information"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8F08C4"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>else</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8F08C4"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(Wizard1.ActiveStepIndex == 1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            Wizard1.HeaderText = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Contact Detail"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8F08C4"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>else</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            Wizard1.HeaderText = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Summary"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3209,6 +3704,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8F08C4"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5267,56 +5768,6 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>531495</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>27305</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9338A8E3-210C-6192-3F85-3C8D9C53EEF8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="17973675"/>
-          <a:ext cx="4798695" cy="3837305"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -5340,7 +5791,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5399,7 +5850,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5458,7 +5909,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -11223,7 +11674,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C7503C0-8239-401F-824D-F448B1640AB9}">
-  <dimension ref="B2:B92"/>
+  <dimension ref="B2:B115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -11264,6 +11715,112 @@
     <row r="92" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B92" s="2" t="s">
         <v>538</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="1"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="1"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="6" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="6" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="6" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="6" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B115" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
+++ b/WebAppCoding/WebAppCoding/C_Sharp_Chapter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C_Sharp\WebAppCoding\WebAppCoding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE4B691-D957-4E1C-9C1F-BADC6A5AE69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF09C7E-DABE-4AD4-A12F-220CF3967A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chapter" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="561">
   <si>
     <t>10 .Text Box</t>
   </si>
@@ -3061,6 +3061,20 @@
   </si>
   <si>
     <r>
+      <t>namespace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> WebAppCoding._37_WizardControl</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>public</t>
     </r>
     <r>
@@ -3552,6 +3566,675 @@
         <family val="3"/>
       </rPr>
       <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>partial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Wizardbtn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> : System.Web.UI.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Page</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>protected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Wizard1_ActiveStepChanged</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>sender</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF2B91AF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>EventArgs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F377F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            Response.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Write</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>"The Activate Index Start with 0 and Clicked Event is :"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> + Wizard1.ActiveStepIndex.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF74531F"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ToString</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>());</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WizardSteps</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">                  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>asp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WizardStep</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>runat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>="server"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>title</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>="Step 1"&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>asp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WizardStep</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>asp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WizardStep</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>runat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>="server"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>title</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>="Step 2"&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>asp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WizardStep</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>runat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>="server"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>title</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>="Step 3"&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>&lt;/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WizardSteps</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
     </r>
   </si>
 </sst>
@@ -3559,7 +4242,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3710,6 +4393,18 @@
       <name val="Cascadia Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF800000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5382,65 +6077,6 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>319405</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>179705</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{889A6332-AB56-0767-671E-81CFA89E7B2C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect t="33908" r="22804" b="9426"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="609600" y="581025"/>
-          <a:ext cx="4586605" cy="1894205"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -5464,7 +6100,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5514,7 +6150,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5564,7 +6200,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5623,7 +6259,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5673,7 +6309,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5732,7 +6368,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5791,7 +6427,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5850,7 +6486,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5909,7 +6545,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6000,56 +6636,6 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>11088</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F64FC17-3BE5-EDF9-E54B-9CBDB83A516B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="2686050"/>
-          <a:ext cx="7086600" cy="2297088"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -6073,7 +6659,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -11682,6 +12268,46 @@
         <v>531</v>
       </c>
     </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>560</v>
+      </c>
+    </row>
     <row r="16" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>532</v>
@@ -11719,7 +12345,7 @@
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
@@ -11729,7 +12355,7 @@
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.25">
@@ -11750,7 +12376,7 @@
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B101" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.25">
@@ -11760,7 +12386,7 @@
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B103" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.25">
@@ -11770,7 +12396,7 @@
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B105" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.25">
@@ -11780,7 +12406,7 @@
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.25">
@@ -11790,7 +12416,7 @@
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B109" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.25">
@@ -11800,7 +12426,7 @@
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B111" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.25">
@@ -11810,7 +12436,7 @@
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.25">
@@ -11834,7 +12460,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75D0CE2-412A-4E45-A15E-28AE503ECBC8}">
-  <dimension ref="B2:B12"/>
+  <dimension ref="B2:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -11845,6 +12471,79 @@
     <row r="12" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>540</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
